--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8941-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8941-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B57EC5A-E793-4911-832A-DF1BC14530DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{899191E0-428F-4262-918D-DD20BF87A4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FB352B22-EEEA-4029-BDDA-EBA97AF7454A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3D8E6EB4-4FED-4E6F-996E-FAD5032FBD95}"/>
   </bookViews>
   <sheets>
     <sheet name="8941-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1499,25 +1499,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E6F845-5C3F-4FA3-8162-71DFD73B8A32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF4A8EB-B977-4D21-B422-85C656B9471A}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" customWidth="1"/>
-    <col min="7" max="9" width="7.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="9" width="9.375" customWidth="1"/>
+    <col min="10" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.375" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1671,7 +1671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>2025</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
         <v>2024</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="45" t="s">
         <v>26</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="46"/>
       <c r="B13" s="22" t="s">
         <v>31</v>
@@ -2135,7 +2135,7 @@
       <c r="Q13" s="50"/>
       <c r="R13" s="50"/>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="43">
         <v>2023</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="41">
         <v>2022</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>2021</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>6.38</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>2020</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <v>2019</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>2018</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <v>2017</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="41">
         <v>2016</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>2015</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>2014</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <v>2013</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>2012</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <v>2011</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <v>2010</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <v>2009</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>2008</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="43">
         <v>2007</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>2006</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="43">
         <v>2005</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>2004</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="43">
         <v>2003</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>2002</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="43">
         <v>2001</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="41">
         <v>2000</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
         <v>37</v>
       </c>
